--- a/supplementary-materials/tables/Table_S12.xlsx
+++ b/supplementary-materials/tables/Table_S12.xlsx
@@ -177,7 +177,7 @@
     <t>At least one positive sample</t>
   </si>
   <si>
-    <t>Posterior predictive probability that any K &gt; 0 in window W</t>
+    <t/>
   </si>
   <si>
     <t>Communicate the chance of at least one retained positive sample</t>
@@ -351,7 +351,7 @@
     <t>5,557 HEX</t>
   </si>
   <si>
-    <t>Planning-facing summary within the retained interpretation tiers</t>
+    <t/>
   </si>
   <si>
     <t>Fitted calling-density parameter</t>
